--- a/laporan_padel_dki_jakarta_2026-10-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-15.xlsx
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp3.160.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp939.000</t>
+          <t>Rp1.064.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp3.045.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.325.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp298.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.196.000</t>
+          <t>Rp996.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.180.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.244.000</t>
+          <t>Rp3.294.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp266.000</t>
+          <t>Rp319.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp10.150.000</t>
+          <t>Rp11.050.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.950.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp42.400.000</t>
+          <t>Rp41.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.100.000</t>
+          <t>Rp9.160.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.245.000</t>
+          <t>Rp4.970.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.575.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp9.975.000</t>
+          <t>Rp8.575.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.421.000</t>
+          <t>Rp6.171.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp13.525.000</t>
+          <t>Rp13.950.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp6.175.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.075.000</t>
+          <t>Rp7.250.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.017.000</t>
+          <t>Rp1.152.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.224.992</t>
+          <t>Rp4.349.992</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.851.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-15.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.725.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.271.000</t>
+          <t>Rp2.359.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.440.000</t>
+          <t>Rp5.920.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.335.988</t>
+          <t>Rp4.536.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.505.000</t>
+          <t>Rp12.711.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp1.510.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.133.000</t>
+          <t>Rp2.571.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp5.125.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.594.000</t>
+          <t>Rp2.496.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp4.430.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.325.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp5.180.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp99.000</t>
+          <t>Rp70.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.580.000</t>
+          <t>Rp5.576.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.781.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.860.000</t>
+          <t>Rp3.080.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.020.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.215.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.512.000</t>
+          <t>Rp14.096.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.200.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.630.000</t>
+          <t>Rp6.815.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.520.000</t>
+          <t>Rp3.640.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp11.900.000</t>
+          <t>Rp12.600.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.994.000</t>
+          <t>Rp1.645.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.385.000</t>
+          <t>Rp1.995.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp34.145.000</t>
+          <t>Rp34.695.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.070.000</t>
+          <t>Rp3.440.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp17.100.000</t>
+          <t>Rp20.100.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.170.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>79</v>
       </c>
       <c r="D49" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.020.000</t>
+          <t>Rp7.905.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp319.000</t>
+          <t>Rp390.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.960.000</t>
+          <t>Rp3.660.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp7.470.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.095.000</t>
+          <t>Rp2.635.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp21.092.500</t>
+          <t>Rp21.917.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp41.000.000</t>
+          <t>Rp41.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.010.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp912.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.160.000</t>
+          <t>Rp9.280.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.835.000</t>
+          <t>Rp11.060.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.620.000</t>
+          <t>Rp12.605.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.625.000</t>
+          <t>Rp9.325.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp18.467.000</t>
+          <t>Rp18.747.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.171.000</t>
+          <t>Rp6.252.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp4.490.000</t>
+          <t>Rp4.710.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.420.000</t>
+          <t>Rp2.705.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp13.950.000</t>
+          <t>Rp14.300.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.144.000</t>
+          <t>Rp5.036.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.175.000</t>
+          <t>Rp6.275.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp21.875.000</t>
+          <t>Rp22.300.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D41" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.860.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.990.000</t>
+          <t>Rp6.710.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.865.000</t>
+          <t>Rp3.635.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.755.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp6.010.000</t>
+          <t>Rp6.390.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.570.000</t>
+          <t>Rp5.770.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.280.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp7.152.000</t>
+          <t>Rp7.252.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.870.000</t>
+          <t>Rp19.710.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.835.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.349.992</t>
+          <t>Rp4.549.991</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.705.000</t>
+          <t>Rp3.927.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.348.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.487.000</t>
+          <t>Rp1.637.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.380.000</t>
+          <t>Rp3.549.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.194.000</t>
+          <t>Rp1.592.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-15.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.660.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.445.000</t>
+          <t>Rp2.895.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.536.987</t>
+          <t>Rp4.866.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.380.000</t>
+          <t>Rp8.630.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -820,24 +820,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp100.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.408.000</t>
+          <t>Rp7.760.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.571.000</t>
+          <t>Rp3.009.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.125.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp240.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.034.000</t>
+          <t>Rp2.322.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.496.000</t>
+          <t>Rp1.911.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.720.000</t>
+          <t>Rp4.890.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.045.000</t>
+          <t>Rp2.630.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.983.000</t>
+          <t>Rp10.383.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.912.000</t>
+          <t>Rp7.488.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp996.000</t>
+          <t>Rp1.195.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp149.000</t>
+          <t>Rp70.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -2435,16 +2435,16 @@
         <v>36</v>
       </c>
       <c r="D65" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.019.000</t>
+          <t>Rp2.682.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.576.000</t>
+          <t>Rp5.078.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp940.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.377.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.390.000</t>
+          <t>Rp2.284.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp4.410.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp3.086.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.096.000</t>
+          <t>Rp14.395.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.095.000</t>
+          <t>Rp4.345.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp12.600.000</t>
+          <t>Rp13.500.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.170.000</t>
+          <t>Rp2.370.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>79</v>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp7.470.000</t>
+          <t>Rp7.690.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp29.500.000</t>
+          <t>Rp28.900.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp9.400.000</t>
+          <t>Rp10.450.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp680.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.420.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp41.750.000</t>
+          <t>Rp42.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp1.190.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.875.000</t>
+          <t>Rp7.115.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp6.789.000</t>
+          <t>Rp3.792.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.280.000</t>
+          <t>Rp9.480.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.162.000</t>
+          <t>Rp6.441.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp8.575.000</t>
+          <t>Rp8.925.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.252.000</t>
+          <t>Rp6.518.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp680.000</t>
+          <t>Rp160.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.039.000</t>
+          <t>Rp6.237.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.705.000</t>
+          <t>Rp3.560.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp9.925.000</t>
+          <t>Rp10.170.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp14.300.000</t>
+          <t>Rp15.100.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>84</v>
       </c>
       <c r="D36" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.275.000</t>
+          <t>Rp7.275.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp22.300.000</t>
+          <t>Rp22.875.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.525.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.250.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.665.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.488.000</t>
+          <t>Rp4.584.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp670.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.120.000</t>
+          <t>Rp2.380.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp6.390.000</t>
+          <t>Rp6.770.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.770.000</t>
+          <t>Rp6.310.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp7.252.000</t>
+          <t>Rp6.602.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.710.000</t>
+          <t>Rp20.590.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.480.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.355.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.265.000</t>
+          <t>Rp1.555.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp2.610.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.637.000</t>
+          <t>Rp2.231.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp6.070.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.549.000</t>
+          <t>Rp3.380.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.592.000</t>
+          <t>Rp1.990.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-15.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.660.000</t>
+          <t>Rp1.820.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.895.000</t>
+          <t>Rp2.295.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.920.000</t>
+          <t>Rp6.160.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.510.000</t>
+          <t>Rp1.930.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.322.000</t>
+          <t>Rp2.730.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.977.000</t>
+          <t>Rp2.397.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.590.000</t>
+          <t>Rp790.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp968.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.180.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2494,24 +2494,24 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D67" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.880.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp160.000 - Rp260.000</t>
+          <t>Rp70.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp378.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp20.100.000</t>
+          <t>Rp19.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.625.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp4.360.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.635.000</t>
+          <t>Rp3.405.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.480.000</t>
+          <t>Rp9.320.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.060.000</t>
+          <t>Rp11.260.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp9.325.000</t>
+          <t>Rp10.725.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.170.000</t>
+          <t>Rp10.660.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp7.275.000</t>
+          <t>Rp7.475.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp820.000</t>
+          <t>Rp1.340.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.287.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.590.000</t>
+          <t>Rp21.070.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.549.991</t>
+          <t>Rp4.749.990</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.425.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.348.000</t>
+          <t>Rp5.745.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-15.xlsx
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.810.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp3.775.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="D80" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.377.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.075.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>36</v>
       </c>
       <c r="D93" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp754.000</t>
+          <t>Rp853.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.905.000</t>
+          <t>Rp8.200.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.855.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.900.000</t>
+          <t>Rp9.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.190.000</t>
+          <t>Rp1.309.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp497.000</t>
+          <t>Rp695.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.000.000</t>
+          <t>Rp17.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp15.100.000</t>
+          <t>Rp15.175.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.036.000</t>
+          <t>Rp5.412.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>84</v>
       </c>
       <c r="D36" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.678.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.755.000</t>
+          <t>Rp4.905.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.310.000</t>
+          <t>Rp6.510.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.749.990</t>
+          <t>Rp4.999.990</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.185.000</t>
+          <t>Rp2.635.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
